--- a/docs/exp.xlsx
+++ b/docs/exp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LaTeX\Лабораторная работа 2.1 - Нелинейные преобразования сигналов\IBTC-physics-3k5s-latex-nonlinear_signal_transformations\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LaTeX\Лабораторная работа 2.1 - Нелинейные преобразования сигналов\IBTC-physics-3k5s-latex-nonlinear_signal_transformations\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B75294-DF7A-484F-B8B9-4F688DE4A343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8847885-61B9-44E4-8BB2-31E6E8C3F283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72DAC28A-CC5D-4E53-B52C-59F617CB31CD}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +92,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="204"/>
@@ -118,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -129,6 +138,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -148,6 +163,769 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'1'!$B$3:$B$81</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="79"/>
+                <c:pt idx="0">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>179.1</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>179.2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>179.3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>179.4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>179.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>179.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>179.7</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>179.8</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>179.9</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>180.1</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>180.2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>180.3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>180.4</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>180.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>180.6</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>180.7</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>180.8</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>180.9</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>210</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'1'!$C$3:$C$81</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="79"/>
+                <c:pt idx="0">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D069-4BC1-9A74-490AE03BF17A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1629637855"/>
+        <c:axId val="1629630175"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1629637855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1629630175"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1629630175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1629637855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -933,7 +1711,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -1367,7 +2145,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -2028,7 +2806,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -2454,7 +3232,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -3105,6 +3883,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -5685,7 +6503,564 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>280148</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>146796</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>67235</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>32496</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61673FC7-8492-3884-1B75-669A3E55C33E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5726,7 +7101,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5767,7 +7142,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5808,7 +7183,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6202,7 +7577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81930DA4-ABA8-4723-B725-D67B44879FEB}">
-  <dimension ref="B2:C81"/>
+  <dimension ref="B2:M81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
@@ -6214,453 +7589,823 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3">
+      <c r="B3" s="6">
         <v>150</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6">
         <v>140</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4">
+      <c r="B4" s="6">
         <v>151</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="6">
         <v>160</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5">
+      <c r="B5" s="6">
         <v>152</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="6">
         <v>160</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6">
+      <c r="B6" s="6">
         <v>153</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>160</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7">
+      <c r="B7" s="6">
         <v>154</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="6">
         <v>160</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8">
+      <c r="B8" s="6">
         <v>155</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="6">
         <v>160</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9">
+      <c r="B9" s="6">
         <v>156</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="6">
         <v>160</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10">
+      <c r="B10" s="6">
         <v>157</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="6">
         <v>180</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11">
+      <c r="B11" s="6">
         <v>158</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="6">
         <v>180</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12">
+      <c r="B12" s="6">
         <v>159</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="6">
         <v>180</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13">
+      <c r="B13" s="6">
         <v>160</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="6">
         <v>180</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14">
+      <c r="B14" s="6">
         <v>161</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="6">
         <v>180</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15">
+      <c r="B15" s="6">
         <v>162</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="6">
         <v>180</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16">
+      <c r="B16" s="6">
         <v>163</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="6">
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="6">
         <v>164</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="6">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="6">
         <v>165</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="6">
         <v>220</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="6">
         <v>166</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="6">
         <v>220</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="6">
         <v>167</v>
       </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21">
+      <c r="C20" s="6">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="6">
         <v>168</v>
       </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22">
+      <c r="C21" s="6">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="6">
         <v>169</v>
       </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23">
+      <c r="C22" s="6">
+        <v>260</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
         <v>170</v>
       </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24">
+      <c r="C23" s="6">
+        <v>280</v>
+      </c>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24" s="6">
         <v>171</v>
       </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25">
+      <c r="C24" s="6">
+        <v>300</v>
+      </c>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25" s="6">
         <v>172</v>
       </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26">
+      <c r="C25" s="6">
+        <v>320</v>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26" s="6">
         <v>173</v>
       </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27">
+      <c r="C26" s="6">
+        <v>340</v>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B27" s="6">
         <v>174</v>
       </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28">
+      <c r="C27" s="6">
+        <v>380</v>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B28" s="6">
         <v>175</v>
       </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29">
+      <c r="C28" s="6">
+        <v>400</v>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B29" s="6">
         <v>176</v>
       </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30">
+      <c r="C29" s="6">
+        <v>460</v>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B30" s="6">
         <v>177</v>
       </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31">
+      <c r="C30" s="6">
+        <v>500</v>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B31" s="6">
         <v>178</v>
       </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32">
+      <c r="C31" s="6">
+        <v>580</v>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B32" s="6">
         <v>179</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33">
+      <c r="C32" s="6">
+        <v>640</v>
+      </c>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B33" s="6">
         <v>179.1</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34">
+      <c r="C33" s="6">
+        <v>640</v>
+      </c>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B34" s="6">
         <v>179.2</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35">
+      <c r="C34" s="6">
+        <v>640</v>
+      </c>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35" s="6">
         <v>179.3</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36">
+      <c r="C35" s="6">
+        <v>640</v>
+      </c>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B36" s="6">
         <v>179.4</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37">
+      <c r="C36" s="6">
+        <v>660</v>
+      </c>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B37" s="6">
         <v>179.5</v>
       </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38">
+      <c r="C37" s="6">
+        <v>660</v>
+      </c>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38" s="6">
         <v>179.6</v>
       </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39">
+      <c r="C38" s="6">
+        <v>660</v>
+      </c>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39" s="6">
         <v>179.7</v>
       </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40">
+      <c r="C39" s="6">
+        <v>660</v>
+      </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B40" s="6">
         <v>179.8</v>
       </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41">
+      <c r="C40" s="6">
+        <v>660</v>
+      </c>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B41" s="6">
         <v>179.9</v>
       </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42">
+      <c r="C41" s="6">
+        <v>640</v>
+      </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B42" s="6">
         <v>180</v>
       </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43">
+      <c r="C42" s="6">
+        <v>60</v>
+      </c>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B43" s="6">
         <v>180.1</v>
       </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B44">
+      <c r="C43" s="6">
+        <v>640</v>
+      </c>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B44" s="6">
         <v>180.2</v>
       </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45">
+      <c r="C44" s="6">
+        <v>660</v>
+      </c>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B45" s="6">
         <v>180.3</v>
       </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B46">
+      <c r="C45" s="6">
+        <v>640</v>
+      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B46" s="6">
         <v>180.4</v>
       </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47">
+      <c r="C46" s="6">
+        <v>640</v>
+      </c>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B47" s="6">
         <v>180.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48">
+      <c r="C47" s="6">
+        <v>640</v>
+      </c>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B48" s="6">
         <v>180.6</v>
       </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49">
+      <c r="C48" s="6">
+        <v>640</v>
+      </c>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B49" s="6">
         <v>180.7</v>
       </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50">
+      <c r="C49" s="6">
+        <v>640</v>
+      </c>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B50" s="6">
         <v>180.8</v>
       </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51">
+      <c r="C50" s="6">
+        <v>640</v>
+      </c>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B51" s="6">
         <v>180.9</v>
       </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52">
+      <c r="C51" s="6">
+        <v>640</v>
+      </c>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B52" s="6">
         <v>181</v>
       </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53">
+      <c r="C52" s="6">
+        <v>640</v>
+      </c>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B53" s="6">
         <v>182</v>
       </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54">
+      <c r="C53" s="6">
+        <v>580</v>
+      </c>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B54" s="6">
         <v>183</v>
       </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55">
+      <c r="C54" s="6">
+        <v>520</v>
+      </c>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B55" s="6">
         <v>184</v>
       </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56">
+      <c r="C55" s="6">
+        <v>440</v>
+      </c>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B56" s="6">
         <v>185</v>
       </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57">
+      <c r="C56" s="6">
+        <v>400</v>
+      </c>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B57" s="6">
         <v>186</v>
       </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58">
+      <c r="C57" s="6">
+        <v>380</v>
+      </c>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B58" s="6">
         <v>187</v>
       </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59">
+      <c r="C58" s="6">
+        <v>340</v>
+      </c>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B59" s="6">
         <v>188</v>
       </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60">
+      <c r="C59" s="6">
+        <v>300</v>
+      </c>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B60" s="6">
         <v>189</v>
       </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61">
+      <c r="C60" s="6">
+        <v>280</v>
+      </c>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61" s="6">
         <v>190</v>
       </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62">
+      <c r="C61" s="6">
+        <v>260</v>
+      </c>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" s="6">
         <v>191</v>
       </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63">
+      <c r="C62" s="6">
+        <v>240</v>
+      </c>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B63" s="6">
         <v>192</v>
       </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64">
+      <c r="C63" s="6">
+        <v>240</v>
+      </c>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B64" s="6">
         <v>193</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65">
+      <c r="C64" s="6">
+        <v>220</v>
+      </c>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B65" s="6">
         <v>194</v>
       </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66">
+      <c r="C65" s="6">
+        <v>220</v>
+      </c>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B66" s="6">
         <v>195</v>
       </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67">
+      <c r="C66" s="6">
+        <v>220</v>
+      </c>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B67" s="6">
         <v>196</v>
       </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68">
+      <c r="C67" s="6">
+        <v>200</v>
+      </c>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B68" s="6">
         <v>197</v>
       </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69">
+      <c r="C68" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B69" s="6">
         <v>198</v>
       </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70">
+      <c r="C69" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B70" s="6">
         <v>199</v>
       </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71">
+      <c r="C70" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B71" s="6">
         <v>200</v>
       </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72">
+      <c r="C71" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B72" s="6">
         <v>201</v>
       </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73">
+      <c r="C72" s="6">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B73" s="6">
         <v>202</v>
       </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74">
+      <c r="C73" s="6">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B74" s="6">
         <v>203</v>
       </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75">
+      <c r="C74" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B75" s="6">
         <v>204</v>
       </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76">
+      <c r="C75" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B76" s="6">
         <v>205</v>
       </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77">
+      <c r="C76" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B77" s="6">
         <v>206</v>
       </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78">
+      <c r="C77" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B78" s="6">
         <v>207</v>
       </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79">
+      <c r="C78" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B79" s="6">
         <v>208</v>
       </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80">
+      <c r="C79" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B80" s="6">
         <v>209</v>
       </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81">
+      <c r="C80" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="6">
         <v>210</v>
+      </c>
+      <c r="C81" s="6">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
